--- a/Documentation/docs/Product Book/PPIQ_Backlog_v2_9_2_08Aug2026.xlsx
+++ b/Documentation/docs/Product Book/PPIQ_Backlog_v2_9_2_08Aug2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\PlantProcess-IQ\Documentation\docs\Product Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99470A47-E62D-4D66-8C35-A960640DFDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16D91E6-950C-47FB-AB5A-E16463E8504D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2995,7 +2995,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3053,12 +3053,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -3102,7 +3096,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3221,16 +3215,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4983,73 +4968,73 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A42" s="44" t="s">
+      <c r="A42" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="B42" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="44" t="s">
+      <c r="B42" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="D42" s="45" t="s">
+      <c r="D42" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="E42" s="44" t="s">
+      <c r="E42" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F42" s="44" t="s">
+      <c r="F42" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="G42" s="44" t="s">
+      <c r="G42" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="46" t="s">
+      <c r="H42" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="I42" s="46" t="s">
+      <c r="I42" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="J42" s="44">
+      <c r="J42" s="41">
         <v>6</v>
       </c>
-      <c r="K42" s="47" t="s">
-        <v>159</v>
+      <c r="K42" s="33" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="19" t="s">
+      <c r="A43" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="B43" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="19" t="s">
+      <c r="B43" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="E43" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F43" s="19" t="s">
+      <c r="F43" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="G43" s="19" t="s">
+      <c r="G43" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="H43" s="36" t="s">
+      <c r="H43" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="I43" s="36" t="s">
+      <c r="I43" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="J43" s="19">
+      <c r="J43" s="41">
         <v>6</v>
       </c>
-      <c r="K43" s="19" t="s">
-        <v>204</v>
+      <c r="K43" s="33" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -5123,7 +5108,7 @@
       </c>
     </row>
     <row r="46" spans="1:11" ht="120" x14ac:dyDescent="0.25">
-      <c r="A46" s="19" t="s">
+      <c r="A46" s="44" t="s">
         <v>214</v>
       </c>
       <c r="B46" s="19" t="s">
@@ -6138,73 +6123,73 @@
       </c>
     </row>
     <row r="75" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A75" s="19" t="s">
+      <c r="A75" s="41" t="s">
         <v>328</v>
       </c>
-      <c r="B75" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="19" t="s">
+      <c r="B75" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="41" t="s">
         <v>310</v>
       </c>
-      <c r="D75" s="38" t="s">
+      <c r="D75" s="42" t="s">
         <v>329</v>
       </c>
-      <c r="E75" s="19" t="s">
+      <c r="E75" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="F75" s="19" t="s">
+      <c r="F75" s="41" t="s">
         <v>318</v>
       </c>
-      <c r="G75" s="19" t="s">
+      <c r="G75" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="H75" s="36" t="s">
+      <c r="H75" s="43" t="s">
         <v>330</v>
       </c>
-      <c r="I75" s="36" t="s">
+      <c r="I75" s="43" t="s">
         <v>331</v>
       </c>
-      <c r="J75" s="19">
+      <c r="J75" s="41">
         <v>4</v>
       </c>
-      <c r="K75" s="19" t="s">
-        <v>204</v>
+      <c r="K75" s="33" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A76" s="19" t="s">
+      <c r="A76" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B76" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="19" t="s">
+      <c r="B76" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="41" t="s">
         <v>310</v>
       </c>
-      <c r="D76" s="38" t="s">
+      <c r="D76" s="42" t="s">
         <v>333</v>
       </c>
-      <c r="E76" s="19" t="s">
+      <c r="E76" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F76" s="19" t="s">
+      <c r="F76" s="41" t="s">
         <v>318</v>
       </c>
-      <c r="G76" s="19" t="s">
+      <c r="G76" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="H76" s="36" t="s">
+      <c r="H76" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="I76" s="36" t="s">
+      <c r="I76" s="43" t="s">
         <v>335</v>
       </c>
-      <c r="J76" s="19">
+      <c r="J76" s="41">
         <v>4</v>
       </c>
-      <c r="K76" s="19" t="s">
-        <v>204</v>
+      <c r="K76" s="33" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -9565,7 +9550,7 @@
       </c>
       <c r="I5" s="22">
         <f>SUMIFS(Backlog!$J$2:$J$168,Backlog!$B$2:$B$168,"M1",Backlog!$K$2:$K$168,"Done")</f>
-        <v>333</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -9594,7 +9579,7 @@
       </c>
       <c r="I6" s="22">
         <f>I4-I5</f>
-        <v>241</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -9623,7 +9608,7 @@
       </c>
       <c r="I7" s="24">
         <f>I5/I4</f>
-        <v>0.58013937282229966</v>
+        <v>0.6149825783972126</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">

--- a/Documentation/docs/Product Book/PPIQ_Backlog_v2_9_2_08Aug2026.xlsx
+++ b/Documentation/docs/Product Book/PPIQ_Backlog_v2_9_2_08Aug2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\PlantProcess-IQ\Documentation\docs\Product Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16D91E6-950C-47FB-AB5A-E16463E8504D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C518A27E-C6AA-421C-8EB4-F1358CED806C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2995,7 +2995,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3053,6 +3053,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -3096,7 +3102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3214,6 +3220,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4649,7 +4667,7 @@
         <v>10</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>159</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="34" customFormat="1" ht="90" x14ac:dyDescent="0.25">
@@ -5038,77 +5056,77 @@
       </c>
     </row>
     <row r="44" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="B44" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="19" t="s">
+      <c r="B44" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="D44" s="38" t="s">
+      <c r="D44" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="E44" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F44" s="19" t="s">
+      <c r="F44" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="G44" s="19" t="s">
+      <c r="G44" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="H44" s="36" t="s">
+      <c r="H44" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="I44" s="36" t="s">
+      <c r="I44" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="J44" s="19">
-        <v>12</v>
-      </c>
-      <c r="K44" s="19" t="s">
-        <v>204</v>
+      <c r="J44" s="41">
+        <v>12</v>
+      </c>
+      <c r="K44" s="33" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="120" x14ac:dyDescent="0.25">
-      <c r="A45" s="19" t="s">
+      <c r="A45" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="B45" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="19" t="s">
+      <c r="B45" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="D45" s="38" t="s">
+      <c r="D45" s="45" t="s">
         <v>793</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="E45" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="F45" s="19" t="s">
+      <c r="F45" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="G45" s="19" t="s">
+      <c r="G45" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="H45" s="36" t="s">
+      <c r="H45" s="46" t="s">
         <v>794</v>
       </c>
-      <c r="I45" s="36" t="s">
+      <c r="I45" s="46" t="s">
         <v>795</v>
       </c>
-      <c r="J45" s="19">
+      <c r="J45" s="44">
         <v>8</v>
       </c>
-      <c r="K45" s="19" t="s">
-        <v>204</v>
+      <c r="K45" s="47" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="120" x14ac:dyDescent="0.25">
-      <c r="A46" s="44" t="s">
+      <c r="A46" s="48" t="s">
         <v>214</v>
       </c>
       <c r="B46" s="19" t="s">
@@ -9550,7 +9568,7 @@
       </c>
       <c r="I5" s="22">
         <f>SUMIFS(Backlog!$J$2:$J$168,Backlog!$B$2:$B$168,"M1",Backlog!$K$2:$K$168,"Done")</f>
-        <v>353</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -9579,7 +9597,7 @@
       </c>
       <c r="I6" s="22">
         <f>I4-I5</f>
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -9608,7 +9626,7 @@
       </c>
       <c r="I7" s="24">
         <f>I5/I4</f>
-        <v>0.6149825783972126</v>
+        <v>0.65331010452961669</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">

--- a/Documentation/docs/Product Book/PPIQ_Backlog_v2_9_2_08Aug2026.xlsx
+++ b/Documentation/docs/Product Book/PPIQ_Backlog_v2_9_2_08Aug2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\PlantProcess-IQ\Documentation\docs\Product Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C518A27E-C6AA-421C-8EB4-F1358CED806C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2CFE0E-E4F0-48A2-94B2-80103B8908D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -516,9 +516,6 @@
     <t>A named test asserts every consistency dimension above and fails the build on any divergence. A deliberate injected divergence - one defect code present in one layer only - makes it fail, proving the gate is switched on. The generator version and seed behind all three layers are identical and recorded. The certification runs in CI rather than by hand, so a later change that breaks consistency is caught by the pipeline rather than in the room. All four retirement-gate conditions are then evidenced in order: the generator reproduces the captured baseline on all nine dimensions; both presentation representations were regenerated from it; this certification passed; and one backup was taken AND RESTORED SUCCESSFULLY. Only then is `src_*` gone, proved by a query returning zero matching schemas, and no obsolete parallel data world remains active anywhere in the presentation database.</t>
   </si>
   <si>
-    <t>InProgress</t>
-  </si>
-  <si>
     <t>T-032</t>
   </si>
   <si>
@@ -2909,6 +2906,9 @@
   <si>
     <t>Presentation Phenomena and Widget Coverage Matrix, 
 part 1: inventory and the 36-chart blueprint</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -3102,7 +3102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3231,9 +3231,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3806,7 +3803,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E8" s="33" t="s">
         <v>15</v>
@@ -4672,7 +4669,7 @@
     </row>
     <row r="33" spans="1:11" s="34" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B33" s="33" t="s">
         <v>12</v>
@@ -4681,22 +4678,22 @@
         <v>151</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E33" s="33" t="s">
         <v>23</v>
       </c>
       <c r="F33" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G33" s="33" t="s">
         <v>17</v>
       </c>
       <c r="H33" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="I33" s="35" t="s">
         <v>163</v>
-      </c>
-      <c r="I33" s="35" t="s">
-        <v>164</v>
       </c>
       <c r="J33" s="33">
         <v>12</v>
@@ -4707,7 +4704,7 @@
     </row>
     <row r="34" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B34" s="33" t="s">
         <v>12</v>
@@ -4716,22 +4713,22 @@
         <v>151</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E34" s="33" t="s">
         <v>23</v>
       </c>
       <c r="F34" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G34" s="33" t="s">
         <v>17</v>
       </c>
       <c r="H34" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="I34" s="35" t="s">
         <v>167</v>
-      </c>
-      <c r="I34" s="35" t="s">
-        <v>168</v>
       </c>
       <c r="J34" s="33">
         <v>12</v>
@@ -4742,7 +4739,7 @@
     </row>
     <row r="35" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="33" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B35" s="33" t="s">
         <v>12</v>
@@ -4751,22 +4748,22 @@
         <v>151</v>
       </c>
       <c r="D35" s="37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E35" s="33" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G35" s="33" t="s">
         <v>71</v>
       </c>
       <c r="H35" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="I35" s="35" t="s">
         <v>171</v>
-      </c>
-      <c r="I35" s="35" t="s">
-        <v>172</v>
       </c>
       <c r="J35" s="33">
         <v>10</v>
@@ -4777,7 +4774,7 @@
     </row>
     <row r="36" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B36" s="33" t="s">
         <v>12</v>
@@ -4786,22 +4783,22 @@
         <v>151</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E36" s="33" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G36" s="33" t="s">
         <v>71</v>
       </c>
       <c r="H36" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="I36" s="35" t="s">
         <v>176</v>
-      </c>
-      <c r="I36" s="35" t="s">
-        <v>177</v>
       </c>
       <c r="J36" s="33">
         <v>8</v>
@@ -4812,7 +4809,7 @@
     </row>
     <row r="37" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B37" s="33" t="s">
         <v>12</v>
@@ -4821,22 +4818,22 @@
         <v>151</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E37" s="33" t="s">
         <v>23</v>
       </c>
       <c r="F37" s="33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G37" s="33" t="s">
         <v>17</v>
       </c>
       <c r="H37" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="I37" s="35" t="s">
         <v>180</v>
-      </c>
-      <c r="I37" s="35" t="s">
-        <v>181</v>
       </c>
       <c r="J37" s="33">
         <v>12</v>
@@ -4847,7 +4844,7 @@
     </row>
     <row r="38" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B38" s="33" t="s">
         <v>12</v>
@@ -4856,22 +4853,22 @@
         <v>151</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E38" s="33" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G38" s="33" t="s">
         <v>35</v>
       </c>
       <c r="H38" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="I38" s="35" t="s">
         <v>184</v>
-      </c>
-      <c r="I38" s="35" t="s">
-        <v>185</v>
       </c>
       <c r="J38" s="33">
         <v>3</v>
@@ -4882,7 +4879,7 @@
     </row>
     <row r="39" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B39" s="33" t="s">
         <v>12</v>
@@ -4891,7 +4888,7 @@
         <v>151</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E39" s="33" t="s">
         <v>23</v>
@@ -4903,10 +4900,10 @@
         <v>17</v>
       </c>
       <c r="H39" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="I39" s="35" t="s">
         <v>188</v>
-      </c>
-      <c r="I39" s="35" t="s">
-        <v>189</v>
       </c>
       <c r="J39" s="33">
         <v>12</v>
@@ -4917,7 +4914,7 @@
     </row>
     <row r="40" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B40" s="33" t="s">
         <v>12</v>
@@ -4926,22 +4923,22 @@
         <v>151</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E40" s="33" t="s">
         <v>59</v>
       </c>
       <c r="F40" s="33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G40" s="33" t="s">
         <v>17</v>
       </c>
       <c r="H40" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="I40" s="35" t="s">
         <v>193</v>
-      </c>
-      <c r="I40" s="35" t="s">
-        <v>194</v>
       </c>
       <c r="J40" s="33">
         <v>12</v>
@@ -4952,7 +4949,7 @@
     </row>
     <row r="41" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B41" s="41" t="s">
         <v>12</v>
@@ -4961,22 +4958,22 @@
         <v>151</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E41" s="41" t="s">
         <v>23</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G41" s="41" t="s">
         <v>71</v>
       </c>
       <c r="H41" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="I41" s="43" t="s">
         <v>197</v>
-      </c>
-      <c r="I41" s="43" t="s">
-        <v>198</v>
       </c>
       <c r="J41" s="41">
         <v>8</v>
@@ -4987,16 +4984,16 @@
     </row>
     <row r="42" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A42" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="B42" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="B42" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="41" t="s">
+      <c r="D42" s="42" t="s">
         <v>200</v>
-      </c>
-      <c r="D42" s="42" t="s">
-        <v>201</v>
       </c>
       <c r="E42" s="41" t="s">
         <v>23</v>
@@ -5008,10 +5005,10 @@
         <v>17</v>
       </c>
       <c r="H42" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="I42" s="43" t="s">
         <v>202</v>
-      </c>
-      <c r="I42" s="43" t="s">
-        <v>203</v>
       </c>
       <c r="J42" s="41">
         <v>6</v>
@@ -5022,16 +5019,16 @@
     </row>
     <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="D43" s="42" t="s">
         <v>205</v>
-      </c>
-      <c r="B43" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="41" t="s">
-        <v>200</v>
-      </c>
-      <c r="D43" s="42" t="s">
-        <v>206</v>
       </c>
       <c r="E43" s="41" t="s">
         <v>23</v>
@@ -5043,10 +5040,10 @@
         <v>17</v>
       </c>
       <c r="H43" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="I43" s="43" t="s">
         <v>207</v>
-      </c>
-      <c r="I43" s="43" t="s">
-        <v>208</v>
       </c>
       <c r="J43" s="41">
         <v>6</v>
@@ -5057,16 +5054,16 @@
     </row>
     <row r="44" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="B44" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="D44" s="42" t="s">
         <v>209</v>
-      </c>
-      <c r="B44" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="41" t="s">
-        <v>200</v>
-      </c>
-      <c r="D44" s="42" t="s">
-        <v>210</v>
       </c>
       <c r="E44" s="41" t="s">
         <v>23</v>
@@ -5078,10 +5075,10 @@
         <v>17</v>
       </c>
       <c r="H44" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="I44" s="43" t="s">
         <v>211</v>
-      </c>
-      <c r="I44" s="43" t="s">
-        <v>212</v>
       </c>
       <c r="J44" s="41">
         <v>12</v>
@@ -5091,122 +5088,122 @@
       </c>
     </row>
     <row r="45" spans="1:11" ht="120" x14ac:dyDescent="0.25">
-      <c r="A45" s="44" t="s">
+      <c r="A45" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="D45" s="42" t="s">
+        <v>792</v>
+      </c>
+      <c r="E45" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="43" t="s">
+        <v>793</v>
+      </c>
+      <c r="I45" s="43" t="s">
+        <v>794</v>
+      </c>
+      <c r="J45" s="41">
+        <v>8</v>
+      </c>
+      <c r="K45" s="33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A46" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="B45" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="44" t="s">
-        <v>200</v>
-      </c>
-      <c r="D45" s="45" t="s">
-        <v>793</v>
-      </c>
-      <c r="E45" s="44" t="s">
+      <c r="B46" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" s="45" t="s">
+        <v>795</v>
+      </c>
+      <c r="E46" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="F45" s="44" t="s">
+      <c r="F46" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="G45" s="44" t="s">
+      <c r="G46" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="H45" s="46" t="s">
-        <v>794</v>
-      </c>
-      <c r="I45" s="46" t="s">
-        <v>795</v>
-      </c>
-      <c r="J45" s="44">
-        <v>8</v>
-      </c>
-      <c r="K45" s="47" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="120" x14ac:dyDescent="0.25">
-      <c r="A46" s="48" t="s">
-        <v>214</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="D46" s="38" t="s">
+      <c r="H46" s="46" t="s">
         <v>796</v>
       </c>
-      <c r="E46" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H46" s="36" t="s">
+      <c r="I46" s="46" t="s">
         <v>797</v>
       </c>
-      <c r="I46" s="36" t="s">
-        <v>798</v>
-      </c>
-      <c r="J46" s="19">
+      <c r="J46" s="44">
         <v>6</v>
       </c>
-      <c r="K46" s="19" t="s">
-        <v>204</v>
+      <c r="K46" s="47" t="s">
+        <v>956</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H47" s="36" t="s">
+        <v>799</v>
+      </c>
+      <c r="I47" s="36" t="s">
         <v>800</v>
-      </c>
-      <c r="I47" s="36" t="s">
-        <v>801</v>
       </c>
       <c r="J47" s="19">
         <v>8</v>
       </c>
       <c r="K47" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E48" s="19" t="s">
         <v>23</v>
@@ -5218,30 +5215,30 @@
         <v>71</v>
       </c>
       <c r="H48" s="36" t="s">
+        <v>802</v>
+      </c>
+      <c r="I48" s="36" t="s">
         <v>803</v>
-      </c>
-      <c r="I48" s="36" t="s">
-        <v>804</v>
       </c>
       <c r="J48" s="19">
         <v>10</v>
       </c>
       <c r="K48" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D49" s="38" t="s">
         <v>218</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="D49" s="38" t="s">
-        <v>219</v>
       </c>
       <c r="E49" s="19" t="s">
         <v>23</v>
@@ -5253,30 +5250,30 @@
         <v>71</v>
       </c>
       <c r="H49" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="I49" s="36" t="s">
         <v>220</v>
-      </c>
-      <c r="I49" s="36" t="s">
-        <v>221</v>
       </c>
       <c r="J49" s="19">
         <v>4</v>
       </c>
       <c r="K49" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="38" t="s">
         <v>222</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="D50" s="38" t="s">
-        <v>223</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>23</v>
@@ -5288,30 +5285,30 @@
         <v>35</v>
       </c>
       <c r="H50" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="I50" s="36" t="s">
         <v>224</v>
-      </c>
-      <c r="I50" s="36" t="s">
-        <v>225</v>
       </c>
       <c r="J50" s="19">
         <v>4</v>
       </c>
       <c r="K50" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" s="38" t="s">
         <v>226</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="D51" s="38" t="s">
-        <v>227</v>
       </c>
       <c r="E51" s="19" t="s">
         <v>23</v>
@@ -5323,30 +5320,30 @@
         <v>71</v>
       </c>
       <c r="H51" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="I51" s="36" t="s">
         <v>228</v>
-      </c>
-      <c r="I51" s="36" t="s">
-        <v>229</v>
       </c>
       <c r="J51" s="19">
         <v>6</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52" s="38" t="s">
         <v>230</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="D52" s="38" t="s">
-        <v>231</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>23</v>
@@ -5358,30 +5355,30 @@
         <v>17</v>
       </c>
       <c r="H52" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="I52" s="36" t="s">
         <v>232</v>
-      </c>
-      <c r="I52" s="36" t="s">
-        <v>233</v>
       </c>
       <c r="J52" s="19">
         <v>6</v>
       </c>
       <c r="K52" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D53" s="38" t="s">
         <v>234</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="D53" s="38" t="s">
-        <v>235</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>23</v>
@@ -5393,30 +5390,30 @@
         <v>17</v>
       </c>
       <c r="H53" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="I53" s="36" t="s">
         <v>236</v>
-      </c>
-      <c r="I53" s="36" t="s">
-        <v>237</v>
       </c>
       <c r="J53" s="19">
         <v>4</v>
       </c>
       <c r="K53" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="B54" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="19" t="s">
+      <c r="D54" s="38" t="s">
         <v>239</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>240</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>23</v>
@@ -5428,205 +5425,205 @@
         <v>17</v>
       </c>
       <c r="H54" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="I54" s="36" t="s">
         <v>241</v>
-      </c>
-      <c r="I54" s="36" t="s">
-        <v>242</v>
       </c>
       <c r="J54" s="19">
         <v>4</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D55" s="38" t="s">
         <v>243</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D55" s="38" t="s">
-        <v>244</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G55" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H55" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="I55" s="36" t="s">
         <v>246</v>
-      </c>
-      <c r="I55" s="36" t="s">
-        <v>247</v>
       </c>
       <c r="J55" s="19">
         <v>4</v>
       </c>
       <c r="K55" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D56" s="38" t="s">
         <v>248</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D56" s="38" t="s">
-        <v>249</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G56" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H56" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="I56" s="36" t="s">
         <v>251</v>
-      </c>
-      <c r="I56" s="36" t="s">
-        <v>252</v>
       </c>
       <c r="J56" s="19">
         <v>6</v>
       </c>
       <c r="K56" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D57" s="38" t="s">
         <v>253</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D57" s="38" t="s">
-        <v>254</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G57" s="19" t="s">
         <v>35</v>
       </c>
       <c r="H57" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="I57" s="36" t="s">
         <v>255</v>
-      </c>
-      <c r="I57" s="36" t="s">
-        <v>256</v>
       </c>
       <c r="J57" s="19">
         <v>4</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D58" s="38" t="s">
         <v>257</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D58" s="38" t="s">
-        <v>258</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G58" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H58" s="36" t="s">
+        <v>259</v>
+      </c>
+      <c r="I58" s="36" t="s">
         <v>260</v>
-      </c>
-      <c r="I58" s="36" t="s">
-        <v>261</v>
       </c>
       <c r="J58" s="19">
         <v>10</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D59" s="38" t="s">
         <v>262</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D59" s="38" t="s">
-        <v>263</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G59" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H59" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="I59" s="36" t="s">
         <v>264</v>
-      </c>
-      <c r="I59" s="36" t="s">
-        <v>265</v>
       </c>
       <c r="J59" s="19">
         <v>10</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D60" s="38" t="s">
         <v>266</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D60" s="38" t="s">
-        <v>267</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>23</v>
@@ -5638,205 +5635,205 @@
         <v>71</v>
       </c>
       <c r="H60" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="I60" s="36" t="s">
         <v>268</v>
-      </c>
-      <c r="I60" s="36" t="s">
-        <v>269</v>
       </c>
       <c r="J60" s="19">
         <v>4</v>
       </c>
       <c r="K60" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D61" s="38" t="s">
         <v>270</v>
-      </c>
-      <c r="B61" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D61" s="38" t="s">
-        <v>271</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G61" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H61" s="36" t="s">
+        <v>271</v>
+      </c>
+      <c r="I61" s="36" t="s">
         <v>272</v>
-      </c>
-      <c r="I61" s="36" t="s">
-        <v>273</v>
       </c>
       <c r="J61" s="19">
         <v>4</v>
       </c>
       <c r="K61" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D62" s="38" t="s">
         <v>274</v>
-      </c>
-      <c r="B62" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D62" s="38" t="s">
-        <v>275</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G62" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H62" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="I62" s="36" t="s">
         <v>277</v>
-      </c>
-      <c r="I62" s="36" t="s">
-        <v>278</v>
       </c>
       <c r="J62" s="19">
         <v>6</v>
       </c>
       <c r="K62" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D63" s="38" t="s">
         <v>279</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D63" s="38" t="s">
-        <v>280</v>
       </c>
       <c r="E63" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G63" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H63" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="I63" s="36" t="s">
         <v>281</v>
-      </c>
-      <c r="I63" s="36" t="s">
-        <v>282</v>
       </c>
       <c r="J63" s="19">
         <v>4</v>
       </c>
       <c r="K63" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D64" s="38" t="s">
         <v>283</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D64" s="38" t="s">
-        <v>284</v>
       </c>
       <c r="E64" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G64" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H64" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="I64" s="36" t="s">
         <v>286</v>
-      </c>
-      <c r="I64" s="36" t="s">
-        <v>287</v>
       </c>
       <c r="J64" s="19">
         <v>10</v>
       </c>
       <c r="K64" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D65" s="38" t="s">
         <v>288</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D65" s="38" t="s">
-        <v>289</v>
       </c>
       <c r="E65" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G65" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H65" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="I65" s="36" t="s">
         <v>291</v>
-      </c>
-      <c r="I65" s="36" t="s">
-        <v>292</v>
       </c>
       <c r="J65" s="19">
         <v>8</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D66" s="38" t="s">
         <v>293</v>
-      </c>
-      <c r="B66" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D66" s="38" t="s">
-        <v>294</v>
       </c>
       <c r="E66" s="19" t="s">
         <v>23</v>
@@ -5848,30 +5845,30 @@
         <v>17</v>
       </c>
       <c r="H66" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="I66" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="I66" s="36" t="s">
-        <v>296</v>
-      </c>
       <c r="J66" s="19">
         <v>12</v>
       </c>
       <c r="K66" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D67" s="38" t="s">
         <v>297</v>
-      </c>
-      <c r="B67" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D67" s="38" t="s">
-        <v>298</v>
       </c>
       <c r="E67" s="19" t="s">
         <v>23</v>
@@ -5883,30 +5880,30 @@
         <v>17</v>
       </c>
       <c r="H67" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="I67" s="36" t="s">
         <v>299</v>
-      </c>
-      <c r="I67" s="36" t="s">
-        <v>300</v>
       </c>
       <c r="J67" s="19">
         <v>6</v>
       </c>
       <c r="K67" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D68" s="38" t="s">
         <v>301</v>
-      </c>
-      <c r="B68" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D68" s="38" t="s">
-        <v>302</v>
       </c>
       <c r="E68" s="19" t="s">
         <v>23</v>
@@ -5918,30 +5915,30 @@
         <v>71</v>
       </c>
       <c r="H68" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="I68" s="36" t="s">
         <v>303</v>
-      </c>
-      <c r="I68" s="36" t="s">
-        <v>304</v>
       </c>
       <c r="J68" s="19">
         <v>8</v>
       </c>
       <c r="K68" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D69" s="38" t="s">
         <v>305</v>
-      </c>
-      <c r="B69" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D69" s="38" t="s">
-        <v>306</v>
       </c>
       <c r="E69" s="19" t="s">
         <v>23</v>
@@ -5953,45 +5950,45 @@
         <v>17</v>
       </c>
       <c r="H69" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="I69" s="36" t="s">
         <v>307</v>
-      </c>
-      <c r="I69" s="36" t="s">
-        <v>308</v>
       </c>
       <c r="J69" s="19">
         <v>6</v>
       </c>
       <c r="K69" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A70" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="B70" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="B70" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" s="33" t="s">
+      <c r="D70" s="37" t="s">
         <v>310</v>
       </c>
-      <c r="D70" s="37" t="s">
+      <c r="E70" s="33" t="s">
         <v>311</v>
       </c>
-      <c r="E70" s="33" t="s">
+      <c r="F70" s="33" t="s">
         <v>312</v>
-      </c>
-      <c r="F70" s="33" t="s">
-        <v>313</v>
       </c>
       <c r="G70" s="33" t="s">
         <v>17</v>
       </c>
       <c r="H70" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="I70" s="35" t="s">
         <v>314</v>
-      </c>
-      <c r="I70" s="35" t="s">
-        <v>315</v>
       </c>
       <c r="J70" s="33">
         <v>8</v>
@@ -6002,31 +5999,31 @@
     </row>
     <row r="71" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A71" s="33" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B71" s="33" t="s">
         <v>12</v>
       </c>
       <c r="C71" s="33" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E71" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="F71" s="33" t="s">
         <v>312</v>
-      </c>
-      <c r="F71" s="33" t="s">
-        <v>313</v>
       </c>
       <c r="G71" s="33" t="s">
         <v>35</v>
       </c>
       <c r="H71" s="35" t="s">
+        <v>805</v>
+      </c>
+      <c r="I71" s="35" t="s">
         <v>806</v>
-      </c>
-      <c r="I71" s="35" t="s">
-        <v>807</v>
       </c>
       <c r="J71" s="33">
         <v>6</v>
@@ -6037,31 +6034,31 @@
     </row>
     <row r="72" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A72" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B72" s="41" t="s">
         <v>12</v>
       </c>
       <c r="C72" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D72" s="42" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E72" s="41" t="s">
         <v>23</v>
       </c>
       <c r="F72" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G72" s="41" t="s">
         <v>17</v>
       </c>
       <c r="H72" s="43" t="s">
+        <v>808</v>
+      </c>
+      <c r="I72" s="43" t="s">
         <v>809</v>
-      </c>
-      <c r="I72" s="43" t="s">
-        <v>810</v>
       </c>
       <c r="J72" s="41">
         <v>8</v>
@@ -6072,31 +6069,31 @@
     </row>
     <row r="73" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="41" t="s">
+        <v>318</v>
+      </c>
+      <c r="B73" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="D73" s="42" t="s">
         <v>319</v>
-      </c>
-      <c r="B73" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" s="41" t="s">
-        <v>310</v>
-      </c>
-      <c r="D73" s="42" t="s">
-        <v>320</v>
       </c>
       <c r="E73" s="41" t="s">
         <v>59</v>
       </c>
       <c r="F73" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G73" s="41" t="s">
         <v>17</v>
       </c>
       <c r="H73" s="43" t="s">
+        <v>320</v>
+      </c>
+      <c r="I73" s="43" t="s">
         <v>321</v>
-      </c>
-      <c r="I73" s="43" t="s">
-        <v>322</v>
       </c>
       <c r="J73" s="41">
         <v>8</v>
@@ -6107,31 +6104,31 @@
     </row>
     <row r="74" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A74" s="41" t="s">
+        <v>322</v>
+      </c>
+      <c r="B74" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="D74" s="42" t="s">
         <v>323</v>
       </c>
-      <c r="B74" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C74" s="41" t="s">
-        <v>310</v>
-      </c>
-      <c r="D74" s="42" t="s">
+      <c r="E74" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="E74" s="41" t="s">
-        <v>325</v>
-      </c>
       <c r="F74" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G74" s="41" t="s">
         <v>17</v>
       </c>
       <c r="H74" s="43" t="s">
+        <v>325</v>
+      </c>
+      <c r="I74" s="43" t="s">
         <v>326</v>
-      </c>
-      <c r="I74" s="43" t="s">
-        <v>327</v>
       </c>
       <c r="J74" s="41">
         <v>8</v>
@@ -6142,31 +6139,31 @@
     </row>
     <row r="75" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="B75" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="D75" s="42" t="s">
         <v>328</v>
-      </c>
-      <c r="B75" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="41" t="s">
-        <v>310</v>
-      </c>
-      <c r="D75" s="42" t="s">
-        <v>329</v>
       </c>
       <c r="E75" s="41" t="s">
         <v>59</v>
       </c>
       <c r="F75" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G75" s="41" t="s">
         <v>71</v>
       </c>
       <c r="H75" s="43" t="s">
+        <v>329</v>
+      </c>
+      <c r="I75" s="43" t="s">
         <v>330</v>
-      </c>
-      <c r="I75" s="43" t="s">
-        <v>331</v>
       </c>
       <c r="J75" s="41">
         <v>4</v>
@@ -6177,31 +6174,31 @@
     </row>
     <row r="76" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="B76" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="D76" s="42" t="s">
         <v>332</v>
-      </c>
-      <c r="B76" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="41" t="s">
-        <v>310</v>
-      </c>
-      <c r="D76" s="42" t="s">
-        <v>333</v>
       </c>
       <c r="E76" s="41" t="s">
         <v>23</v>
       </c>
       <c r="F76" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G76" s="41" t="s">
         <v>71</v>
       </c>
       <c r="H76" s="43" t="s">
+        <v>333</v>
+      </c>
+      <c r="I76" s="43" t="s">
         <v>334</v>
-      </c>
-      <c r="I76" s="43" t="s">
-        <v>335</v>
       </c>
       <c r="J76" s="41">
         <v>4</v>
@@ -6212,296 +6209,296 @@
     </row>
     <row r="77" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="D77" s="38" t="s">
         <v>336</v>
-      </c>
-      <c r="B77" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C77" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D77" s="38" t="s">
-        <v>337</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H77" s="36" t="s">
+        <v>337</v>
+      </c>
+      <c r="I77" s="36" t="s">
         <v>338</v>
-      </c>
-      <c r="I77" s="36" t="s">
-        <v>339</v>
       </c>
       <c r="J77" s="19">
         <v>4</v>
       </c>
       <c r="K77" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="D78" s="38" t="s">
         <v>340</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D78" s="38" t="s">
-        <v>341</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>53</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H78" s="36" t="s">
+        <v>342</v>
+      </c>
+      <c r="I78" s="36" t="s">
         <v>343</v>
-      </c>
-      <c r="I78" s="36" t="s">
-        <v>344</v>
       </c>
       <c r="J78" s="19">
         <v>6</v>
       </c>
       <c r="K78" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="D79" s="38" t="s">
         <v>345</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D79" s="38" t="s">
-        <v>346</v>
       </c>
       <c r="E79" s="19" t="s">
         <v>53</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G79" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H79" s="36" t="s">
+        <v>347</v>
+      </c>
+      <c r="I79" s="36" t="s">
         <v>348</v>
-      </c>
-      <c r="I79" s="36" t="s">
-        <v>349</v>
       </c>
       <c r="J79" s="19">
         <v>4</v>
       </c>
       <c r="K79" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="D80" s="38" t="s">
         <v>350</v>
-      </c>
-      <c r="B80" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D80" s="38" t="s">
-        <v>351</v>
       </c>
       <c r="E80" s="19" t="s">
         <v>53</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H80" s="36" t="s">
+        <v>351</v>
+      </c>
+      <c r="I80" s="36" t="s">
         <v>352</v>
-      </c>
-      <c r="I80" s="36" t="s">
-        <v>353</v>
       </c>
       <c r="J80" s="19">
         <v>3</v>
       </c>
       <c r="K80" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="D81" s="38" t="s">
         <v>354</v>
-      </c>
-      <c r="B81" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C81" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D81" s="38" t="s">
-        <v>355</v>
       </c>
       <c r="E81" s="19" t="s">
         <v>53</v>
       </c>
       <c r="F81" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G81" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H81" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="I81" s="36" t="s">
         <v>357</v>
-      </c>
-      <c r="I81" s="36" t="s">
-        <v>358</v>
       </c>
       <c r="J81" s="19">
         <v>4</v>
       </c>
       <c r="K81" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="D82" s="38" t="s">
         <v>359</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D82" s="38" t="s">
-        <v>360</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F82" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G82" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H82" s="36" t="s">
+        <v>361</v>
+      </c>
+      <c r="I82" s="36" t="s">
         <v>362</v>
-      </c>
-      <c r="I82" s="36" t="s">
-        <v>363</v>
       </c>
       <c r="J82" s="19">
         <v>6</v>
       </c>
       <c r="K82" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="D83" s="38" t="s">
         <v>364</v>
-      </c>
-      <c r="B83" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D83" s="38" t="s">
-        <v>365</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G83" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H83" s="36" t="s">
+        <v>365</v>
+      </c>
+      <c r="I83" s="36" t="s">
         <v>366</v>
-      </c>
-      <c r="I83" s="36" t="s">
-        <v>367</v>
       </c>
       <c r="J83" s="19">
         <v>4</v>
       </c>
       <c r="K83" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="D84" s="38" t="s">
         <v>368</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C84" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D84" s="38" t="s">
-        <v>369</v>
       </c>
       <c r="E84" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F84" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G84" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H84" s="36" t="s">
+        <v>369</v>
+      </c>
+      <c r="I84" s="36" t="s">
         <v>370</v>
-      </c>
-      <c r="I84" s="36" t="s">
-        <v>371</v>
       </c>
       <c r="J84" s="19">
         <v>6</v>
       </c>
       <c r="K84" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="B85" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="C85" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="D85" s="38" t="s">
         <v>374</v>
-      </c>
-      <c r="D85" s="38" t="s">
-        <v>375</v>
       </c>
       <c r="E85" s="19" t="s">
         <v>28</v>
@@ -6513,30 +6510,30 @@
         <v>17</v>
       </c>
       <c r="H85" s="36" t="s">
+        <v>375</v>
+      </c>
+      <c r="I85" s="36" t="s">
         <v>376</v>
-      </c>
-      <c r="I85" s="36" t="s">
-        <v>377</v>
       </c>
       <c r="J85" s="19">
         <v>10</v>
       </c>
       <c r="K85" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D86" s="38" t="s">
         <v>378</v>
-      </c>
-      <c r="B86" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D86" s="38" t="s">
-        <v>379</v>
       </c>
       <c r="E86" s="19" t="s">
         <v>40</v>
@@ -6548,30 +6545,30 @@
         <v>17</v>
       </c>
       <c r="H86" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="I86" s="36" t="s">
         <v>380</v>
-      </c>
-      <c r="I86" s="36" t="s">
-        <v>381</v>
       </c>
       <c r="J86" s="19">
         <v>10</v>
       </c>
       <c r="K86" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="210" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D87" s="38" t="s">
         <v>382</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D87" s="38" t="s">
-        <v>383</v>
       </c>
       <c r="E87" s="19" t="s">
         <v>53</v>
@@ -6583,2235 +6580,2235 @@
         <v>17</v>
       </c>
       <c r="H87" s="36" t="s">
+        <v>383</v>
+      </c>
+      <c r="I87" s="36" t="s">
         <v>384</v>
-      </c>
-      <c r="I87" s="36" t="s">
-        <v>385</v>
       </c>
       <c r="J87" s="19">
         <v>8</v>
       </c>
       <c r="K87" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D88" s="38" t="s">
         <v>386</v>
-      </c>
-      <c r="B88" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C88" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D88" s="38" t="s">
-        <v>387</v>
       </c>
       <c r="E88" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F88" s="19" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G88" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H88" s="36" t="s">
+        <v>388</v>
+      </c>
+      <c r="I88" s="36" t="s">
         <v>389</v>
       </c>
-      <c r="I88" s="36" t="s">
-        <v>390</v>
-      </c>
       <c r="J88" s="19">
         <v>12</v>
       </c>
       <c r="K88" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D89" s="38" t="s">
         <v>391</v>
-      </c>
-      <c r="B89" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D89" s="38" t="s">
-        <v>392</v>
       </c>
       <c r="E89" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F89" s="19" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G89" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H89" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="I89" s="36" t="s">
         <v>393</v>
       </c>
-      <c r="I89" s="36" t="s">
-        <v>394</v>
-      </c>
       <c r="J89" s="19">
         <v>12</v>
       </c>
       <c r="K89" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D90" s="38" t="s">
         <v>395</v>
-      </c>
-      <c r="B90" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C90" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D90" s="38" t="s">
-        <v>396</v>
       </c>
       <c r="E90" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F90" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G90" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H90" s="36" t="s">
+        <v>396</v>
+      </c>
+      <c r="I90" s="36" t="s">
         <v>397</v>
       </c>
-      <c r="I90" s="36" t="s">
-        <v>398</v>
-      </c>
       <c r="J90" s="19">
         <v>12</v>
       </c>
       <c r="K90" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D91" s="38" t="s">
         <v>399</v>
-      </c>
-      <c r="B91" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D91" s="38" t="s">
-        <v>400</v>
       </c>
       <c r="E91" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F91" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G91" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H91" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="I91" s="36" t="s">
         <v>401</v>
       </c>
-      <c r="I91" s="36" t="s">
-        <v>402</v>
-      </c>
       <c r="J91" s="19">
         <v>12</v>
       </c>
       <c r="K91" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D92" s="38" t="s">
         <v>403</v>
-      </c>
-      <c r="B92" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C92" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D92" s="38" t="s">
-        <v>404</v>
       </c>
       <c r="E92" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F92" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G92" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H92" s="36" t="s">
+        <v>404</v>
+      </c>
+      <c r="I92" s="36" t="s">
         <v>405</v>
       </c>
-      <c r="I92" s="36" t="s">
-        <v>406</v>
-      </c>
       <c r="J92" s="19">
         <v>12</v>
       </c>
       <c r="K92" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D93" s="38" t="s">
         <v>407</v>
-      </c>
-      <c r="B93" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C93" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D93" s="38" t="s">
-        <v>408</v>
       </c>
       <c r="E93" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F93" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G93" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H93" s="36" t="s">
+        <v>408</v>
+      </c>
+      <c r="I93" s="36" t="s">
         <v>409</v>
       </c>
-      <c r="I93" s="36" t="s">
-        <v>410</v>
-      </c>
       <c r="J93" s="19">
         <v>12</v>
       </c>
       <c r="K93" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C94" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D94" s="38" t="s">
         <v>411</v>
-      </c>
-      <c r="B94" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C94" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D94" s="38" t="s">
-        <v>412</v>
       </c>
       <c r="E94" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F94" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G94" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H94" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="I94" s="36" t="s">
         <v>413</v>
-      </c>
-      <c r="I94" s="36" t="s">
-        <v>414</v>
       </c>
       <c r="J94" s="19">
         <v>6</v>
       </c>
       <c r="K94" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D95" s="38" t="s">
         <v>415</v>
-      </c>
-      <c r="B95" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D95" s="38" t="s">
-        <v>416</v>
       </c>
       <c r="E95" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F95" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G95" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H95" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="I95" s="36" t="s">
         <v>417</v>
-      </c>
-      <c r="I95" s="36" t="s">
-        <v>418</v>
       </c>
       <c r="J95" s="19">
         <v>8</v>
       </c>
       <c r="K95" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C96" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="B96" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C96" s="19" t="s">
+      <c r="D96" s="38" t="s">
         <v>420</v>
-      </c>
-      <c r="D96" s="38" t="s">
-        <v>421</v>
       </c>
       <c r="E96" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F96" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G96" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H96" s="36" t="s">
+        <v>421</v>
+      </c>
+      <c r="I96" s="36" t="s">
         <v>422</v>
       </c>
-      <c r="I96" s="36" t="s">
-        <v>423</v>
-      </c>
       <c r="J96" s="19">
         <v>12</v>
       </c>
       <c r="K96" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="B97" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D97" s="38" t="s">
         <v>424</v>
-      </c>
-      <c r="B97" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C97" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D97" s="38" t="s">
-        <v>425</v>
       </c>
       <c r="E97" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F97" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G97" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H97" s="36" t="s">
+        <v>425</v>
+      </c>
+      <c r="I97" s="36" t="s">
         <v>426</v>
-      </c>
-      <c r="I97" s="36" t="s">
-        <v>427</v>
       </c>
       <c r="J97" s="19">
         <v>8</v>
       </c>
       <c r="K97" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D98" s="38" t="s">
         <v>428</v>
-      </c>
-      <c r="B98" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D98" s="38" t="s">
-        <v>429</v>
       </c>
       <c r="E98" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F98" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G98" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H98" s="36" t="s">
+        <v>429</v>
+      </c>
+      <c r="I98" s="36" t="s">
         <v>430</v>
-      </c>
-      <c r="I98" s="36" t="s">
-        <v>431</v>
       </c>
       <c r="J98" s="19">
         <v>6</v>
       </c>
       <c r="K98" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D99" s="38" t="s">
         <v>432</v>
-      </c>
-      <c r="B99" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C99" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D99" s="38" t="s">
-        <v>433</v>
       </c>
       <c r="E99" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F99" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G99" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H99" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I99" s="36" t="s">
         <v>434</v>
       </c>
-      <c r="I99" s="36" t="s">
-        <v>435</v>
-      </c>
       <c r="J99" s="19">
         <v>12</v>
       </c>
       <c r="K99" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C100" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D100" s="38" t="s">
         <v>436</v>
-      </c>
-      <c r="B100" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C100" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D100" s="38" t="s">
-        <v>437</v>
       </c>
       <c r="E100" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F100" s="19" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G100" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H100" s="36" t="s">
+        <v>438</v>
+      </c>
+      <c r="I100" s="36" t="s">
         <v>439</v>
-      </c>
-      <c r="I100" s="36" t="s">
-        <v>440</v>
       </c>
       <c r="J100" s="19">
         <v>8</v>
       </c>
       <c r="K100" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C101" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D101" s="38" t="s">
         <v>441</v>
-      </c>
-      <c r="B101" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D101" s="38" t="s">
-        <v>442</v>
       </c>
       <c r="E101" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F101" s="19" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G101" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H101" s="36" t="s">
+        <v>442</v>
+      </c>
+      <c r="I101" s="36" t="s">
         <v>443</v>
-      </c>
-      <c r="I101" s="36" t="s">
-        <v>444</v>
       </c>
       <c r="J101" s="19">
         <v>6</v>
       </c>
       <c r="K101" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C102" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D102" s="38" t="s">
         <v>445</v>
-      </c>
-      <c r="B102" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C102" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D102" s="38" t="s">
-        <v>446</v>
       </c>
       <c r="E102" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F102" s="19" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G102" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H102" s="36" t="s">
+        <v>446</v>
+      </c>
+      <c r="I102" s="36" t="s">
         <v>447</v>
       </c>
-      <c r="I102" s="36" t="s">
-        <v>448</v>
-      </c>
       <c r="J102" s="19">
         <v>12</v>
       </c>
       <c r="K102" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D103" s="38" t="s">
         <v>449</v>
-      </c>
-      <c r="B103" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D103" s="38" t="s">
-        <v>450</v>
       </c>
       <c r="E103" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F103" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G103" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H103" s="36" t="s">
+        <v>450</v>
+      </c>
+      <c r="I103" s="36" t="s">
         <v>451</v>
-      </c>
-      <c r="I103" s="36" t="s">
-        <v>452</v>
       </c>
       <c r="J103" s="19">
         <v>8</v>
       </c>
       <c r="K103" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C104" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D104" s="38" t="s">
         <v>453</v>
-      </c>
-      <c r="B104" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D104" s="38" t="s">
-        <v>454</v>
       </c>
       <c r="E104" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F104" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G104" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H104" s="36" t="s">
+        <v>454</v>
+      </c>
+      <c r="I104" s="36" t="s">
         <v>455</v>
-      </c>
-      <c r="I104" s="36" t="s">
-        <v>456</v>
       </c>
       <c r="J104" s="19">
         <v>6</v>
       </c>
       <c r="K104" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D105" s="38" t="s">
         <v>457</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D105" s="38" t="s">
-        <v>458</v>
       </c>
       <c r="E105" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F105" s="19" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G105" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H105" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="I105" s="36" t="s">
         <v>460</v>
-      </c>
-      <c r="I105" s="36" t="s">
-        <v>461</v>
       </c>
       <c r="J105" s="19">
         <v>8</v>
       </c>
       <c r="K105" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D106" s="38" t="s">
         <v>462</v>
-      </c>
-      <c r="B106" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C106" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D106" s="38" t="s">
-        <v>463</v>
       </c>
       <c r="E106" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F106" s="19" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G106" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H106" s="36" t="s">
+        <v>463</v>
+      </c>
+      <c r="I106" s="36" t="s">
         <v>464</v>
-      </c>
-      <c r="I106" s="36" t="s">
-        <v>465</v>
       </c>
       <c r="J106" s="19">
         <v>6</v>
       </c>
       <c r="K106" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C107" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="B107" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C107" s="19" t="s">
+      <c r="D107" s="38" t="s">
         <v>467</v>
-      </c>
-      <c r="D107" s="38" t="s">
-        <v>468</v>
       </c>
       <c r="E107" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F107" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G107" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H107" s="36" t="s">
+        <v>468</v>
+      </c>
+      <c r="I107" s="36" t="s">
         <v>469</v>
       </c>
-      <c r="I107" s="36" t="s">
-        <v>470</v>
-      </c>
       <c r="J107" s="19">
         <v>12</v>
       </c>
       <c r="K107" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D108" s="38" t="s">
         <v>471</v>
-      </c>
-      <c r="B108" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C108" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D108" s="38" t="s">
-        <v>472</v>
       </c>
       <c r="E108" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F108" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G108" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H108" s="36" t="s">
+        <v>472</v>
+      </c>
+      <c r="I108" s="36" t="s">
         <v>473</v>
       </c>
-      <c r="I108" s="36" t="s">
-        <v>474</v>
-      </c>
       <c r="J108" s="19">
         <v>12</v>
       </c>
       <c r="K108" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D109" s="38" t="s">
         <v>475</v>
-      </c>
-      <c r="B109" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C109" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D109" s="38" t="s">
-        <v>476</v>
       </c>
       <c r="E109" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F109" s="19" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G109" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H109" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="I109" s="36" t="s">
         <v>478</v>
-      </c>
-      <c r="I109" s="36" t="s">
-        <v>479</v>
       </c>
       <c r="J109" s="19">
         <v>8</v>
       </c>
       <c r="K109" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C110" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D110" s="38" t="s">
         <v>480</v>
-      </c>
-      <c r="B110" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D110" s="38" t="s">
-        <v>481</v>
       </c>
       <c r="E110" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F110" s="19" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G110" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H110" s="36" t="s">
+        <v>481</v>
+      </c>
+      <c r="I110" s="36" t="s">
         <v>482</v>
-      </c>
-      <c r="I110" s="36" t="s">
-        <v>483</v>
       </c>
       <c r="J110" s="19">
         <v>6</v>
       </c>
       <c r="K110" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C111" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D111" s="38" t="s">
         <v>484</v>
-      </c>
-      <c r="B111" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C111" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D111" s="38" t="s">
-        <v>485</v>
       </c>
       <c r="E111" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F111" s="19" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G111" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H111" s="36" t="s">
+        <v>485</v>
+      </c>
+      <c r="I111" s="36" t="s">
         <v>486</v>
       </c>
-      <c r="I111" s="36" t="s">
-        <v>487</v>
-      </c>
       <c r="J111" s="19">
         <v>12</v>
       </c>
       <c r="K111" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C112" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D112" s="38" t="s">
         <v>488</v>
-      </c>
-      <c r="B112" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C112" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D112" s="38" t="s">
-        <v>489</v>
       </c>
       <c r="E112" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F112" s="19" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G112" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H112" s="36" t="s">
+        <v>490</v>
+      </c>
+      <c r="I112" s="36" t="s">
         <v>491</v>
       </c>
-      <c r="I112" s="36" t="s">
-        <v>492</v>
-      </c>
       <c r="J112" s="19">
         <v>12</v>
       </c>
       <c r="K112" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D113" s="38" t="s">
         <v>493</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D113" s="38" t="s">
-        <v>494</v>
       </c>
       <c r="E113" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F113" s="19" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G113" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H113" s="36" t="s">
+        <v>495</v>
+      </c>
+      <c r="I113" s="36" t="s">
         <v>496</v>
       </c>
-      <c r="I113" s="36" t="s">
-        <v>497</v>
-      </c>
       <c r="J113" s="19">
         <v>12</v>
       </c>
       <c r="K113" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D114" s="38" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E114" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F114" s="19" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G114" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H114" s="36" t="s">
+        <v>811</v>
+      </c>
+      <c r="I114" s="36" t="s">
         <v>812</v>
-      </c>
-      <c r="I114" s="36" t="s">
-        <v>813</v>
       </c>
       <c r="J114" s="19">
         <v>8</v>
       </c>
       <c r="K114" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D115" s="38" t="s">
         <v>499</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D115" s="38" t="s">
-        <v>500</v>
       </c>
       <c r="E115" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F115" s="19" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G115" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H115" s="36" t="s">
+        <v>500</v>
+      </c>
+      <c r="I115" s="36" t="s">
         <v>501</v>
-      </c>
-      <c r="I115" s="36" t="s">
-        <v>502</v>
       </c>
       <c r="J115" s="19">
         <v>6</v>
       </c>
       <c r="K115" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D116" s="38" t="s">
         <v>503</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C116" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D116" s="38" t="s">
-        <v>504</v>
       </c>
       <c r="E116" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F116" s="19" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G116" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H116" s="36" t="s">
+        <v>504</v>
+      </c>
+      <c r="I116" s="36" t="s">
         <v>505</v>
-      </c>
-      <c r="I116" s="36" t="s">
-        <v>506</v>
       </c>
       <c r="J116" s="19">
         <v>4</v>
       </c>
       <c r="K116" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D117" s="38" t="s">
         <v>507</v>
-      </c>
-      <c r="B117" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C117" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D117" s="38" t="s">
-        <v>508</v>
       </c>
       <c r="E117" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F117" s="19" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G117" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H117" s="36" t="s">
+        <v>509</v>
+      </c>
+      <c r="I117" s="36" t="s">
         <v>510</v>
-      </c>
-      <c r="I117" s="36" t="s">
-        <v>511</v>
       </c>
       <c r="J117" s="19">
         <v>8</v>
       </c>
       <c r="K117" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
+        <v>511</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D118" s="38" t="s">
         <v>512</v>
-      </c>
-      <c r="B118" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C118" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D118" s="38" t="s">
-        <v>513</v>
       </c>
       <c r="E118" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F118" s="19" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G118" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H118" s="36" t="s">
+        <v>513</v>
+      </c>
+      <c r="I118" s="36" t="s">
         <v>514</v>
-      </c>
-      <c r="I118" s="36" t="s">
-        <v>515</v>
       </c>
       <c r="J118" s="19">
         <v>6</v>
       </c>
       <c r="K118" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C119" s="19" t="s">
         <v>516</v>
       </c>
-      <c r="B119" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C119" s="19" t="s">
+      <c r="D119" s="38" t="s">
         <v>517</v>
-      </c>
-      <c r="D119" s="38" t="s">
-        <v>518</v>
       </c>
       <c r="E119" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F119" s="19" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G119" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H119" s="36" t="s">
+        <v>519</v>
+      </c>
+      <c r="I119" s="36" t="s">
         <v>520</v>
       </c>
-      <c r="I119" s="36" t="s">
-        <v>521</v>
-      </c>
       <c r="J119" s="19">
         <v>12</v>
       </c>
       <c r="K119" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C120" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="D120" s="38" t="s">
         <v>522</v>
-      </c>
-      <c r="B120" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C120" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="D120" s="38" t="s">
-        <v>523</v>
       </c>
       <c r="E120" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F120" s="19" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G120" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H120" s="36" t="s">
+        <v>524</v>
+      </c>
+      <c r="I120" s="36" t="s">
         <v>525</v>
       </c>
-      <c r="I120" s="36" t="s">
-        <v>526</v>
-      </c>
       <c r="J120" s="19">
         <v>12</v>
       </c>
       <c r="K120" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
+        <v>526</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="D121" s="38" t="s">
         <v>527</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C121" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="D121" s="38" t="s">
-        <v>528</v>
       </c>
       <c r="E121" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F121" s="19" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G121" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H121" s="36" t="s">
+        <v>528</v>
+      </c>
+      <c r="I121" s="36" t="s">
         <v>529</v>
       </c>
-      <c r="I121" s="36" t="s">
-        <v>530</v>
-      </c>
       <c r="J121" s="19">
         <v>12</v>
       </c>
       <c r="K121" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C122" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="D122" s="38" t="s">
         <v>531</v>
-      </c>
-      <c r="B122" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C122" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="D122" s="38" t="s">
-        <v>532</v>
       </c>
       <c r="E122" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F122" s="19" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G122" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H122" s="36" t="s">
+        <v>533</v>
+      </c>
+      <c r="I122" s="36" t="s">
         <v>534</v>
       </c>
-      <c r="I122" s="36" t="s">
-        <v>535</v>
-      </c>
       <c r="J122" s="19">
         <v>12</v>
       </c>
       <c r="K122" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="D123" s="38" t="s">
         <v>536</v>
-      </c>
-      <c r="B123" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C123" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="D123" s="38" t="s">
-        <v>537</v>
       </c>
       <c r="E123" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F123" s="19" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G123" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H123" s="36" t="s">
+        <v>538</v>
+      </c>
+      <c r="I123" s="36" t="s">
         <v>539</v>
       </c>
-      <c r="I123" s="36" t="s">
-        <v>540</v>
-      </c>
       <c r="J123" s="19">
         <v>12</v>
       </c>
       <c r="K123" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="D124" s="38" t="s">
         <v>541</v>
-      </c>
-      <c r="B124" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C124" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="D124" s="38" t="s">
-        <v>542</v>
       </c>
       <c r="E124" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F124" s="19" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G124" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H124" s="36" t="s">
+        <v>542</v>
+      </c>
+      <c r="I124" s="36" t="s">
         <v>543</v>
       </c>
-      <c r="I124" s="36" t="s">
-        <v>544</v>
-      </c>
       <c r="J124" s="19">
         <v>12</v>
       </c>
       <c r="K124" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="D125" s="38" t="s">
         <v>545</v>
-      </c>
-      <c r="B125" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C125" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="D125" s="38" t="s">
-        <v>546</v>
       </c>
       <c r="E125" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F125" s="19" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G125" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H125" s="36" t="s">
+        <v>547</v>
+      </c>
+      <c r="I125" s="36" t="s">
         <v>548</v>
       </c>
-      <c r="I125" s="36" t="s">
-        <v>549</v>
-      </c>
       <c r="J125" s="19">
         <v>12</v>
       </c>
       <c r="K125" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="D126" s="38" t="s">
         <v>550</v>
-      </c>
-      <c r="B126" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C126" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="D126" s="38" t="s">
-        <v>551</v>
       </c>
       <c r="E126" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F126" s="19" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G126" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H126" s="36" t="s">
+        <v>551</v>
+      </c>
+      <c r="I126" s="36" t="s">
         <v>552</v>
       </c>
-      <c r="I126" s="36" t="s">
-        <v>553</v>
-      </c>
       <c r="J126" s="19">
         <v>12</v>
       </c>
       <c r="K126" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="D127" s="38" t="s">
         <v>554</v>
-      </c>
-      <c r="B127" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C127" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="D127" s="38" t="s">
-        <v>555</v>
       </c>
       <c r="E127" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F127" s="19" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G127" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H127" s="36" t="s">
+        <v>556</v>
+      </c>
+      <c r="I127" s="36" t="s">
         <v>557</v>
       </c>
-      <c r="I127" s="36" t="s">
-        <v>558</v>
-      </c>
       <c r="J127" s="19">
         <v>12</v>
       </c>
       <c r="K127" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
+        <v>558</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C128" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="D128" s="38" t="s">
         <v>559</v>
-      </c>
-      <c r="B128" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C128" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="D128" s="38" t="s">
-        <v>560</v>
       </c>
       <c r="E128" s="19" t="s">
         <v>53</v>
       </c>
       <c r="F128" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G128" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H128" s="36" t="s">
+        <v>560</v>
+      </c>
+      <c r="I128" s="36" t="s">
         <v>561</v>
       </c>
-      <c r="I128" s="36" t="s">
-        <v>562</v>
-      </c>
       <c r="J128" s="19">
         <v>12</v>
       </c>
       <c r="K128" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
+        <v>562</v>
+      </c>
+      <c r="B129" s="19" t="s">
         <v>563</v>
       </c>
-      <c r="B129" s="19" t="s">
+      <c r="C129" s="19" t="s">
         <v>564</v>
       </c>
-      <c r="C129" s="19" t="s">
+      <c r="D129" s="38" t="s">
         <v>565</v>
       </c>
-      <c r="D129" s="38" t="s">
+      <c r="E129" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F129" s="19" t="s">
         <v>566</v>
-      </c>
-      <c r="E129" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="F129" s="19" t="s">
-        <v>567</v>
       </c>
       <c r="G129" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H129" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="I129" s="36" t="s">
         <v>568</v>
       </c>
-      <c r="I129" s="36" t="s">
-        <v>569</v>
-      </c>
       <c r="J129" s="19">
         <v>12</v>
       </c>
       <c r="K129" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C130" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D130" s="38" t="s">
         <v>570</v>
       </c>
-      <c r="B130" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C130" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D130" s="38" t="s">
-        <v>571</v>
-      </c>
       <c r="E130" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F130" s="19" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G130" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H130" s="36" t="s">
+        <v>571</v>
+      </c>
+      <c r="I130" s="36" t="s">
         <v>572</v>
       </c>
-      <c r="I130" s="36" t="s">
-        <v>573</v>
-      </c>
       <c r="J130" s="19">
         <v>12</v>
       </c>
       <c r="K130" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
+        <v>573</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C131" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D131" s="38" t="s">
         <v>574</v>
       </c>
-      <c r="B131" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C131" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D131" s="38" t="s">
+      <c r="E131" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F131" s="19" t="s">
         <v>575</v>
-      </c>
-      <c r="E131" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="F131" s="19" t="s">
-        <v>576</v>
       </c>
       <c r="G131" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H131" s="36" t="s">
+        <v>576</v>
+      </c>
+      <c r="I131" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="I131" s="36" t="s">
-        <v>578</v>
-      </c>
       <c r="J131" s="19">
         <v>12</v>
       </c>
       <c r="K131" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
+        <v>578</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C132" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D132" s="38" t="s">
         <v>579</v>
       </c>
-      <c r="B132" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C132" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D132" s="38" t="s">
+      <c r="E132" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F132" s="19" t="s">
         <v>580</v>
-      </c>
-      <c r="E132" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="F132" s="19" t="s">
-        <v>581</v>
       </c>
       <c r="G132" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H132" s="36" t="s">
+        <v>581</v>
+      </c>
+      <c r="I132" s="36" t="s">
         <v>582</v>
       </c>
-      <c r="I132" s="36" t="s">
-        <v>583</v>
-      </c>
       <c r="J132" s="19">
         <v>12</v>
       </c>
       <c r="K132" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
+        <v>583</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D133" s="38" t="s">
         <v>584</v>
       </c>
-      <c r="B133" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C133" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D133" s="38" t="s">
-        <v>585</v>
-      </c>
       <c r="E133" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F133" s="19" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G133" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H133" s="36" t="s">
+        <v>585</v>
+      </c>
+      <c r="I133" s="36" t="s">
         <v>586</v>
       </c>
-      <c r="I133" s="36" t="s">
-        <v>587</v>
-      </c>
       <c r="J133" s="19">
         <v>12</v>
       </c>
       <c r="K133" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="B134" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C134" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D134" s="38" t="s">
         <v>588</v>
       </c>
-      <c r="B134" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C134" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D134" s="38" t="s">
-        <v>589</v>
-      </c>
       <c r="E134" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F134" s="19" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G134" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H134" s="36" t="s">
+        <v>589</v>
+      </c>
+      <c r="I134" s="36" t="s">
         <v>590</v>
       </c>
-      <c r="I134" s="36" t="s">
-        <v>591</v>
-      </c>
       <c r="J134" s="19">
         <v>12</v>
       </c>
       <c r="K134" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C135" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D135" s="38" t="s">
         <v>592</v>
       </c>
-      <c r="B135" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C135" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D135" s="38" t="s">
-        <v>593</v>
-      </c>
       <c r="E135" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F135" s="19" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G135" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H135" s="36" t="s">
+        <v>593</v>
+      </c>
+      <c r="I135" s="36" t="s">
         <v>594</v>
       </c>
-      <c r="I135" s="36" t="s">
-        <v>595</v>
-      </c>
       <c r="J135" s="19">
         <v>12</v>
       </c>
       <c r="K135" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
+        <v>595</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C136" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D136" s="38" t="s">
         <v>596</v>
-      </c>
-      <c r="B136" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C136" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D136" s="38" t="s">
-        <v>597</v>
       </c>
       <c r="E136" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F136" s="19" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G136" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H136" s="36" t="s">
+        <v>597</v>
+      </c>
+      <c r="I136" s="36" t="s">
         <v>598</v>
-      </c>
-      <c r="I136" s="36" t="s">
-        <v>599</v>
       </c>
       <c r="J136" s="19">
         <v>10</v>
       </c>
       <c r="K136" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="B137" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C137" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D137" s="38" t="s">
         <v>600</v>
       </c>
-      <c r="B137" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C137" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D137" s="38" t="s">
-        <v>601</v>
-      </c>
       <c r="E137" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F137" s="19" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G137" s="19" t="s">
         <v>35</v>
       </c>
       <c r="H137" s="36" t="s">
+        <v>601</v>
+      </c>
+      <c r="I137" s="36" t="s">
         <v>602</v>
-      </c>
-      <c r="I137" s="36" t="s">
-        <v>603</v>
       </c>
       <c r="J137" s="19">
         <v>10</v>
       </c>
       <c r="K137" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C138" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D138" s="38" t="s">
         <v>604</v>
       </c>
-      <c r="B138" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C138" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D138" s="38" t="s">
+      <c r="E138" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F138" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="G138" s="19" t="s">
         <v>605</v>
       </c>
-      <c r="E138" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="F138" s="19" t="s">
-        <v>318</v>
-      </c>
-      <c r="G138" s="19" t="s">
+      <c r="H138" s="36" t="s">
         <v>606</v>
       </c>
-      <c r="H138" s="36" t="s">
+      <c r="I138" s="36" t="s">
         <v>607</v>
-      </c>
-      <c r="I138" s="36" t="s">
-        <v>608</v>
       </c>
       <c r="J138" s="19">
         <v>3</v>
       </c>
       <c r="K138" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
+        <v>608</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D139" s="38" t="s">
         <v>609</v>
       </c>
-      <c r="B139" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C139" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D139" s="38" t="s">
-        <v>610</v>
-      </c>
       <c r="E139" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F139" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G139" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H139" s="36" t="s">
+        <v>610</v>
+      </c>
+      <c r="I139" s="36" t="s">
         <v>611</v>
       </c>
-      <c r="I139" s="36" t="s">
-        <v>612</v>
-      </c>
       <c r="J139" s="19">
         <v>12</v>
       </c>
       <c r="K139" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C140" s="19" t="s">
         <v>613</v>
       </c>
-      <c r="B140" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C140" s="19" t="s">
+      <c r="D140" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="D140" s="38" t="s">
+      <c r="E140" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F140" s="19" t="s">
         <v>615</v>
-      </c>
-      <c r="E140" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="F140" s="19" t="s">
-        <v>616</v>
       </c>
       <c r="G140" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H140" s="36" t="s">
+        <v>616</v>
+      </c>
+      <c r="I140" s="36" t="s">
         <v>617</v>
       </c>
-      <c r="I140" s="36" t="s">
-        <v>618</v>
-      </c>
       <c r="J140" s="19">
         <v>12</v>
       </c>
       <c r="K140" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
+        <v>618</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D141" s="38" t="s">
         <v>619</v>
       </c>
-      <c r="B141" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C141" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="D141" s="38" t="s">
-        <v>620</v>
-      </c>
       <c r="E141" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F141" s="19" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G141" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H141" s="36" t="s">
+        <v>620</v>
+      </c>
+      <c r="I141" s="36" t="s">
         <v>621</v>
       </c>
-      <c r="I141" s="36" t="s">
-        <v>622</v>
-      </c>
       <c r="J141" s="19">
         <v>12</v>
       </c>
       <c r="K141" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
+        <v>622</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D142" s="38" t="s">
         <v>623</v>
       </c>
-      <c r="B142" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C142" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="D142" s="38" t="s">
-        <v>624</v>
-      </c>
       <c r="E142" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F142" s="19" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G142" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H142" s="36" t="s">
+        <v>624</v>
+      </c>
+      <c r="I142" s="36" t="s">
         <v>625</v>
       </c>
-      <c r="I142" s="36" t="s">
-        <v>626</v>
-      </c>
       <c r="J142" s="19">
         <v>12</v>
       </c>
       <c r="K142" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
+        <v>626</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D143" s="38" t="s">
         <v>627</v>
       </c>
-      <c r="B143" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C143" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="D143" s="38" t="s">
+      <c r="E143" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F143" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="E143" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="F143" s="19" t="s">
-        <v>629</v>
       </c>
       <c r="G143" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H143" s="36" t="s">
+        <v>629</v>
+      </c>
+      <c r="I143" s="36" t="s">
         <v>630</v>
-      </c>
-      <c r="I143" s="36" t="s">
-        <v>631</v>
       </c>
       <c r="J143" s="19">
         <v>6</v>
       </c>
       <c r="K143" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C144" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D144" s="38" t="s">
         <v>632</v>
       </c>
-      <c r="B144" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C144" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="D144" s="38" t="s">
-        <v>633</v>
-      </c>
       <c r="E144" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F144" s="19" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G144" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H144" s="36" t="s">
+        <v>633</v>
+      </c>
+      <c r="I144" s="36" t="s">
         <v>634</v>
-      </c>
-      <c r="I144" s="36" t="s">
-        <v>635</v>
       </c>
       <c r="J144" s="19">
         <v>8</v>
       </c>
       <c r="K144" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D145" s="38" t="s">
         <v>636</v>
       </c>
-      <c r="B145" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C145" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="D145" s="38" t="s">
+      <c r="E145" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F145" s="19" t="s">
         <v>637</v>
-      </c>
-      <c r="E145" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="F145" s="19" t="s">
-        <v>638</v>
       </c>
       <c r="G145" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H145" s="36" t="s">
+        <v>638</v>
+      </c>
+      <c r="I145" s="36" t="s">
         <v>639</v>
-      </c>
-      <c r="I145" s="36" t="s">
-        <v>640</v>
       </c>
       <c r="J145" s="19">
         <v>8</v>
       </c>
       <c r="K145" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
+        <v>640</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D146" s="38" t="s">
         <v>641</v>
       </c>
-      <c r="B146" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C146" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="D146" s="38" t="s">
-        <v>642</v>
-      </c>
       <c r="E146" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F146" s="19" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G146" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H146" s="36" t="s">
+        <v>642</v>
+      </c>
+      <c r="I146" s="36" t="s">
         <v>643</v>
-      </c>
-      <c r="I146" s="36" t="s">
-        <v>644</v>
       </c>
       <c r="J146" s="19">
         <v>6</v>
       </c>
       <c r="K146" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B147" s="19" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D147" s="38" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E147" s="19" t="s">
         <v>65</v>
       </c>
       <c r="F147" s="19" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G147" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H147" s="36" t="s">
+        <v>814</v>
+      </c>
+      <c r="I147" s="36" t="s">
         <v>815</v>
       </c>
-      <c r="I147" s="36" t="s">
-        <v>816</v>
-      </c>
       <c r="J147" s="19">
         <v>12</v>
       </c>
       <c r="K147" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B148" s="19" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D148" s="38" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E148" s="19" t="s">
         <v>65</v>
       </c>
       <c r="F148" s="19" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G148" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H148" s="36" t="s">
+        <v>817</v>
+      </c>
+      <c r="I148" s="36" t="s">
         <v>818</v>
       </c>
-      <c r="I148" s="36" t="s">
-        <v>819</v>
-      </c>
       <c r="J148" s="19">
         <v>12</v>
       </c>
       <c r="K148" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
+        <v>647</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D149" s="38" t="s">
         <v>648</v>
-      </c>
-      <c r="B149" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C149" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="D149" s="38" t="s">
-        <v>649</v>
       </c>
       <c r="E149" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F149" s="19" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G149" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H149" s="36" t="s">
+        <v>649</v>
+      </c>
+      <c r="I149" s="36" t="s">
         <v>650</v>
-      </c>
-      <c r="I149" s="36" t="s">
-        <v>651</v>
       </c>
       <c r="J149" s="19">
         <v>8</v>
       </c>
       <c r="K149" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D150" s="38" t="s">
         <v>652</v>
-      </c>
-      <c r="B150" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C150" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="D150" s="38" t="s">
-        <v>653</v>
       </c>
       <c r="E150" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F150" s="19" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G150" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H150" s="36" t="s">
+        <v>653</v>
+      </c>
+      <c r="I150" s="36" t="s">
         <v>654</v>
-      </c>
-      <c r="I150" s="36" t="s">
-        <v>655</v>
       </c>
       <c r="J150" s="19">
         <v>6</v>
       </c>
       <c r="K150" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="151" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B151" s="19" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D151" s="38" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E151" s="19" t="s">
         <v>53</v>
@@ -8823,611 +8820,611 @@
         <v>17</v>
       </c>
       <c r="H151" s="36" t="s">
+        <v>820</v>
+      </c>
+      <c r="I151" s="36" t="s">
         <v>821</v>
       </c>
-      <c r="I151" s="36" t="s">
-        <v>822</v>
-      </c>
       <c r="J151" s="19">
         <v>12</v>
       </c>
       <c r="K151" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
+        <v>656</v>
+      </c>
+      <c r="B152" s="19" t="s">
         <v>657</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="C152" s="19" t="s">
         <v>658</v>
       </c>
-      <c r="C152" s="19" t="s">
+      <c r="D152" s="38" t="s">
         <v>659</v>
-      </c>
-      <c r="D152" s="38" t="s">
-        <v>660</v>
       </c>
       <c r="E152" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F152" s="19" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G152" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H152" s="36" t="s">
+        <v>661</v>
+      </c>
+      <c r="I152" s="36" t="s">
         <v>662</v>
       </c>
-      <c r="I152" s="36" t="s">
-        <v>663</v>
-      </c>
       <c r="J152" s="19">
         <v>12</v>
       </c>
       <c r="K152" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
+        <v>663</v>
+      </c>
+      <c r="B153" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C153" s="19" t="s">
+        <v>658</v>
+      </c>
+      <c r="D153" s="38" t="s">
         <v>664</v>
-      </c>
-      <c r="B153" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C153" s="19" t="s">
-        <v>659</v>
-      </c>
-      <c r="D153" s="38" t="s">
-        <v>665</v>
       </c>
       <c r="E153" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F153" s="19" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G153" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H153" s="36" t="s">
+        <v>665</v>
+      </c>
+      <c r="I153" s="36" t="s">
         <v>666</v>
       </c>
-      <c r="I153" s="36" t="s">
-        <v>667</v>
-      </c>
       <c r="J153" s="19">
         <v>12</v>
       </c>
       <c r="K153" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="19" t="s">
+        <v>667</v>
+      </c>
+      <c r="B154" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C154" s="19" t="s">
+        <v>658</v>
+      </c>
+      <c r="D154" s="38" t="s">
         <v>668</v>
-      </c>
-      <c r="B154" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C154" s="19" t="s">
-        <v>659</v>
-      </c>
-      <c r="D154" s="38" t="s">
-        <v>669</v>
       </c>
       <c r="E154" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F154" s="19" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G154" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H154" s="36" t="s">
+        <v>670</v>
+      </c>
+      <c r="I154" s="36" t="s">
         <v>671</v>
       </c>
-      <c r="I154" s="36" t="s">
-        <v>672</v>
-      </c>
       <c r="J154" s="19">
         <v>12</v>
       </c>
       <c r="K154" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="B155" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C155" s="19" t="s">
+        <v>658</v>
+      </c>
+      <c r="D155" s="38" t="s">
         <v>673</v>
-      </c>
-      <c r="B155" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C155" s="19" t="s">
-        <v>659</v>
-      </c>
-      <c r="D155" s="38" t="s">
-        <v>674</v>
       </c>
       <c r="E155" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F155" s="19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G155" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H155" s="36" t="s">
+        <v>675</v>
+      </c>
+      <c r="I155" s="36" t="s">
         <v>676</v>
       </c>
-      <c r="I155" s="36" t="s">
-        <v>677</v>
-      </c>
       <c r="J155" s="19">
         <v>12</v>
       </c>
       <c r="K155" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="19" t="s">
+        <v>677</v>
+      </c>
+      <c r="B156" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C156" s="19" t="s">
+        <v>658</v>
+      </c>
+      <c r="D156" s="38" t="s">
         <v>678</v>
-      </c>
-      <c r="B156" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C156" s="19" t="s">
-        <v>659</v>
-      </c>
-      <c r="D156" s="38" t="s">
-        <v>679</v>
       </c>
       <c r="E156" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F156" s="19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G156" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H156" s="36" t="s">
+        <v>679</v>
+      </c>
+      <c r="I156" s="36" t="s">
         <v>680</v>
       </c>
-      <c r="I156" s="36" t="s">
-        <v>681</v>
-      </c>
       <c r="J156" s="19">
         <v>12</v>
       </c>
       <c r="K156" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="B157" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C157" s="19" t="s">
+        <v>658</v>
+      </c>
+      <c r="D157" s="38" t="s">
         <v>682</v>
-      </c>
-      <c r="B157" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C157" s="19" t="s">
-        <v>659</v>
-      </c>
-      <c r="D157" s="38" t="s">
-        <v>683</v>
       </c>
       <c r="E157" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F157" s="19" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G157" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H157" s="36" t="s">
+        <v>684</v>
+      </c>
+      <c r="I157" s="36" t="s">
         <v>685</v>
       </c>
-      <c r="I157" s="36" t="s">
-        <v>686</v>
-      </c>
       <c r="J157" s="19">
         <v>12</v>
       </c>
       <c r="K157" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="19" t="s">
+        <v>686</v>
+      </c>
+      <c r="B158" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C158" s="19" t="s">
+        <v>658</v>
+      </c>
+      <c r="D158" s="38" t="s">
         <v>687</v>
       </c>
-      <c r="B158" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C158" s="19" t="s">
-        <v>659</v>
-      </c>
-      <c r="D158" s="38" t="s">
+      <c r="E158" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F158" s="19" t="s">
         <v>688</v>
-      </c>
-      <c r="E158" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="F158" s="19" t="s">
-        <v>689</v>
       </c>
       <c r="G158" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H158" s="36" t="s">
+        <v>689</v>
+      </c>
+      <c r="I158" s="36" t="s">
         <v>690</v>
       </c>
-      <c r="I158" s="36" t="s">
-        <v>691</v>
-      </c>
       <c r="J158" s="19">
         <v>12</v>
       </c>
       <c r="K158" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="19" t="s">
+        <v>691</v>
+      </c>
+      <c r="B159" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C159" s="19" t="s">
+        <v>658</v>
+      </c>
+      <c r="D159" s="38" t="s">
         <v>692</v>
       </c>
-      <c r="B159" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C159" s="19" t="s">
-        <v>659</v>
-      </c>
-      <c r="D159" s="38" t="s">
-        <v>693</v>
-      </c>
       <c r="E159" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F159" s="19" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G159" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H159" s="36" t="s">
+        <v>693</v>
+      </c>
+      <c r="I159" s="36" t="s">
         <v>694</v>
       </c>
-      <c r="I159" s="36" t="s">
-        <v>695</v>
-      </c>
       <c r="J159" s="19">
         <v>12</v>
       </c>
       <c r="K159" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="19" t="s">
+        <v>695</v>
+      </c>
+      <c r="B160" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C160" s="19" t="s">
         <v>696</v>
       </c>
-      <c r="B160" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C160" s="19" t="s">
+      <c r="D160" s="38" t="s">
         <v>697</v>
-      </c>
-      <c r="D160" s="38" t="s">
-        <v>698</v>
       </c>
       <c r="E160" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F160" s="19" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G160" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H160" s="36" t="s">
+        <v>699</v>
+      </c>
+      <c r="I160" s="36" t="s">
         <v>700</v>
       </c>
-      <c r="I160" s="36" t="s">
-        <v>701</v>
-      </c>
       <c r="J160" s="19">
         <v>12</v>
       </c>
       <c r="K160" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="19" t="s">
+        <v>701</v>
+      </c>
+      <c r="B161" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C161" s="19" t="s">
+        <v>696</v>
+      </c>
+      <c r="D161" s="38" t="s">
         <v>702</v>
-      </c>
-      <c r="B161" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C161" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="D161" s="38" t="s">
-        <v>703</v>
       </c>
       <c r="E161" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F161" s="19" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G161" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H161" s="36" t="s">
+        <v>704</v>
+      </c>
+      <c r="I161" s="36" t="s">
         <v>705</v>
       </c>
-      <c r="I161" s="36" t="s">
-        <v>706</v>
-      </c>
       <c r="J161" s="19">
         <v>12</v>
       </c>
       <c r="K161" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="19" t="s">
+        <v>706</v>
+      </c>
+      <c r="B162" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C162" s="19" t="s">
+        <v>696</v>
+      </c>
+      <c r="D162" s="38" t="s">
         <v>707</v>
-      </c>
-      <c r="B162" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C162" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="D162" s="38" t="s">
-        <v>708</v>
       </c>
       <c r="E162" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F162" s="19" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G162" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H162" s="36" t="s">
+        <v>708</v>
+      </c>
+      <c r="I162" s="36" t="s">
         <v>709</v>
       </c>
-      <c r="I162" s="36" t="s">
-        <v>710</v>
-      </c>
       <c r="J162" s="19">
         <v>12</v>
       </c>
       <c r="K162" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="19" t="s">
+        <v>710</v>
+      </c>
+      <c r="B163" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C163" s="19" t="s">
+        <v>696</v>
+      </c>
+      <c r="D163" s="38" t="s">
         <v>711</v>
-      </c>
-      <c r="B163" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C163" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="D163" s="38" t="s">
-        <v>712</v>
       </c>
       <c r="E163" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F163" s="19" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G163" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H163" s="36" t="s">
+        <v>712</v>
+      </c>
+      <c r="I163" s="36" t="s">
         <v>713</v>
       </c>
-      <c r="I163" s="36" t="s">
-        <v>714</v>
-      </c>
       <c r="J163" s="19">
         <v>12</v>
       </c>
       <c r="K163" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="19" t="s">
+        <v>714</v>
+      </c>
+      <c r="B164" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C164" s="19" t="s">
+        <v>696</v>
+      </c>
+      <c r="D164" s="38" t="s">
         <v>715</v>
-      </c>
-      <c r="B164" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C164" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="D164" s="38" t="s">
-        <v>716</v>
       </c>
       <c r="E164" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F164" s="19" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G164" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H164" s="36" t="s">
+        <v>716</v>
+      </c>
+      <c r="I164" s="36" t="s">
         <v>717</v>
       </c>
-      <c r="I164" s="36" t="s">
-        <v>718</v>
-      </c>
       <c r="J164" s="19">
         <v>12</v>
       </c>
       <c r="K164" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="19" t="s">
+        <v>718</v>
+      </c>
+      <c r="B165" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C165" s="19" t="s">
+        <v>696</v>
+      </c>
+      <c r="D165" s="38" t="s">
         <v>719</v>
-      </c>
-      <c r="B165" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C165" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="D165" s="38" t="s">
-        <v>720</v>
       </c>
       <c r="E165" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F165" s="19" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G165" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H165" s="36" t="s">
+        <v>721</v>
+      </c>
+      <c r="I165" s="36" t="s">
         <v>722</v>
       </c>
-      <c r="I165" s="36" t="s">
-        <v>723</v>
-      </c>
       <c r="J165" s="19">
         <v>12</v>
       </c>
       <c r="K165" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="B166" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C166" s="19" t="s">
+        <v>696</v>
+      </c>
+      <c r="D166" s="38" t="s">
         <v>724</v>
-      </c>
-      <c r="B166" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C166" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="D166" s="38" t="s">
-        <v>725</v>
       </c>
       <c r="E166" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F166" s="19" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G166" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H166" s="36" t="s">
+        <v>726</v>
+      </c>
+      <c r="I166" s="36" t="s">
         <v>727</v>
       </c>
-      <c r="I166" s="36" t="s">
-        <v>728</v>
-      </c>
       <c r="J166" s="19">
         <v>12</v>
       </c>
       <c r="K166" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A167" s="19" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B167" s="19" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D167" s="38" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E167" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F167" s="19" t="s">
         <v>312</v>
-      </c>
-      <c r="F167" s="19" t="s">
-        <v>313</v>
       </c>
       <c r="G167" s="19" t="s">
         <v>35</v>
       </c>
       <c r="H167" s="36" t="s">
+        <v>823</v>
+      </c>
+      <c r="I167" s="36" t="s">
         <v>824</v>
       </c>
-      <c r="I167" s="36" t="s">
-        <v>825</v>
-      </c>
       <c r="J167" s="19">
         <v>12</v>
       </c>
       <c r="K167" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="19" t="s">
+        <v>729</v>
+      </c>
+      <c r="B168" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="C168" s="19" t="s">
+        <v>696</v>
+      </c>
+      <c r="D168" s="38" t="s">
         <v>730</v>
-      </c>
-      <c r="B168" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C168" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="D168" s="38" t="s">
-        <v>731</v>
       </c>
       <c r="E168" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F168" s="19" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G168" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H168" s="36" t="s">
+        <v>731</v>
+      </c>
+      <c r="I168" s="36" t="s">
         <v>732</v>
       </c>
-      <c r="I168" s="36" t="s">
-        <v>733</v>
-      </c>
       <c r="J168" s="19">
         <v>12</v>
       </c>
       <c r="K168" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -9455,16 +9452,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>737</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>9</v>
@@ -9478,10 +9475,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>738</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>739</v>
       </c>
       <c r="E2" s="1">
         <f>COUNTIF(Backlog!C:C,A2)</f>
@@ -9500,10 +9497,10 @@
         <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>740</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>741</v>
       </c>
       <c r="E3" s="1">
         <f>COUNTIF(Backlog!C:C,A3)</f>
@@ -9522,10 +9519,10 @@
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>742</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>743</v>
       </c>
       <c r="E4" s="1">
         <f>COUNTIF(Backlog!C:C,A4)</f>
@@ -9536,7 +9533,7 @@
         <v>107</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="I4" s="22">
         <v>574</v>
@@ -9544,16 +9541,16 @@
     </row>
     <row r="5" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>744</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>745</v>
       </c>
       <c r="E5" s="1">
         <f>COUNTIF(Backlog!C:C,A5)</f>
@@ -9564,25 +9561,25 @@
         <v>80</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I5" s="22">
         <f>SUMIFS(Backlog!$J$2:$J$168,Backlog!$B$2:$B$168,"M1",Backlog!$K$2:$K$168,"Done")</f>
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>747</v>
       </c>
       <c r="E6" s="1">
         <f>COUNTIF(Backlog!C:C,A6)</f>
@@ -9593,25 +9590,25 @@
         <v>106</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I6" s="22">
         <f>I4-I5</f>
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>748</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="E7" s="1">
         <f>COUNTIF(Backlog!C:C,A7)</f>
@@ -9622,25 +9619,25 @@
         <v>83</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="I7" s="24">
         <f>I5/I4</f>
-        <v>0.65331010452961669</v>
+        <v>0.66724738675958184</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>750</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>751</v>
       </c>
       <c r="E8" s="1">
         <f>COUNTIF(Backlog!C:C,A8)</f>
@@ -9653,16 +9650,16 @@
     </row>
     <row r="9" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>752</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>753</v>
       </c>
       <c r="E9" s="1">
         <f>COUNTIF(Backlog!C:C,A9)</f>
@@ -9675,16 +9672,16 @@
     </row>
     <row r="10" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>754</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>755</v>
       </c>
       <c r="E10" s="1">
         <f>COUNTIF(Backlog!C:C,A10)</f>
@@ -9697,16 +9694,16 @@
     </row>
     <row r="11" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>756</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>757</v>
       </c>
       <c r="E11" s="1">
         <f>COUNTIF(Backlog!C:C,A11)</f>
@@ -9719,16 +9716,16 @@
     </row>
     <row r="12" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>758</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>759</v>
       </c>
       <c r="E12" s="1">
         <f>COUNTIF(Backlog!C:C,A12)</f>
@@ -9741,16 +9738,16 @@
     </row>
     <row r="13" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>761</v>
       </c>
       <c r="E13" s="1">
         <f>COUNTIF(Backlog!C:C,A13)</f>
@@ -9763,16 +9760,16 @@
     </row>
     <row r="14" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="E14" s="1">
         <f>COUNTIF(Backlog!C:C,A14)</f>
@@ -9785,16 +9782,16 @@
     </row>
     <row r="15" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>764</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>765</v>
       </c>
       <c r="E15" s="1">
         <f>COUNTIF(Backlog!C:C,A15)</f>
@@ -9807,7 +9804,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C16" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E16" s="7">
         <f>SUM(E2:E15)</f>
@@ -9837,13 +9834,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -9860,7 +9857,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C2" s="1">
         <f>COUNTIF(Backlog!B:B,A2)</f>
@@ -9881,10 +9878,10 @@
     </row>
     <row r="3" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C3" s="1">
         <f>COUNTIF(Backlog!B:B,A3)</f>
@@ -9905,10 +9902,10 @@
     </row>
     <row r="4" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C4" s="1">
         <f>COUNTIF(Backlog!B:B,A4)</f>
@@ -9929,10 +9926,10 @@
     </row>
     <row r="5" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C5" s="1">
         <f>COUNTIF(Backlog!B:B,A5)</f>
@@ -9953,7 +9950,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(C2:C5)</f>
@@ -9980,15 +9977,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
+        <v>770</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>771</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9996,7 +9993,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10004,7 +10001,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10012,7 +10009,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10020,7 +10017,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10028,23 +10025,23 @@
         <v>9</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
+        <v>777</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>778</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
+        <v>779</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>780</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10053,34 +10050,34 @@
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
+        <v>781</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>782</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
+        <v>783</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>784</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
+        <v>785</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>786</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
+        <v>787</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>788</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10089,50 +10086,50 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
+        <v>789</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>790</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
+        <v>832</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>833</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
+        <v>834</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>835</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
+        <v>836</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>837</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
+        <v>838</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>839</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>840</v>
       </c>
     </row>
   </sheetData>
@@ -10157,7 +10154,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -10165,15 +10162,15 @@
       <c r="E1" s="29"/>
       <c r="F1" s="29"/>
       <c r="H1" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="I1" s="25" t="s">
         <v>842</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -10181,7 +10178,7 @@
       <c r="E2" s="30"/>
       <c r="F2" s="30"/>
       <c r="H2" s="27" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I2" s="28">
         <f>COUNTA(A8:A38)</f>
@@ -10190,7 +10187,7 @@
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H3" s="27" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I3" s="28">
         <f>COUNTIF(E8:E38,"NEW TASK REQUIRED")</f>
@@ -10199,7 +10196,7 @@
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H4" s="27" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="I4" s="28">
         <f>COUNTIF(E8:E38,"EXPANDED")</f>
@@ -10208,7 +10205,7 @@
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H5" s="27" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I5" s="28">
         <f>COUNTIF(E8:E38,"EXISTING")</f>
@@ -10217,7 +10214,7 @@
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H6" s="27" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I6" s="28">
         <f>COUNTIF(E8:E38,"GLOBAL LAW")</f>
@@ -10226,430 +10223,430 @@
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="B7" s="26" t="s">
         <v>850</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="C7" s="26" t="s">
         <v>851</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="D7" s="26" t="s">
         <v>852</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="E7" s="26" t="s">
         <v>853</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="F7" s="26" t="s">
         <v>854</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
+        <v>855</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>856</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="C8" s="18" t="s">
+        <v>644</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>857</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>645</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>614</v>
-      </c>
-      <c r="E8" s="18" t="s">
+      <c r="F8" s="18" t="s">
         <v>858</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
+        <v>859</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>860</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="C9" s="18" t="s">
+        <v>644</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>857</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>861</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>645</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>614</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
+        <v>862</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>863</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="C10" s="18" t="s">
+        <v>646</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="E10" s="18" t="s">
         <v>864</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>647</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>614</v>
-      </c>
-      <c r="E10" s="18" t="s">
+      <c r="F10" s="18" t="s">
         <v>865</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
+        <v>866</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>867</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="C11" s="18" t="s">
         <v>868</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="D11" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>864</v>
+      </c>
+      <c r="F11" s="18" t="s">
         <v>869</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>865</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
+        <v>870</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>871</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="C12" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>857</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>872</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
+        <v>873</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>874</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="C13" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>857</v>
+      </c>
+      <c r="F13" s="18" t="s">
         <v>875</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
+        <v>876</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>877</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="C14" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>857</v>
+      </c>
+      <c r="F14" s="18" t="s">
         <v>878</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
+        <v>879</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>880</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="C15" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>857</v>
+      </c>
+      <c r="F15" s="18" t="s">
         <v>881</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
+        <v>882</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>883</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="C16" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>857</v>
+      </c>
+      <c r="F16" s="18" t="s">
         <v>884</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
+        <v>885</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>886</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="C17" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>864</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>887</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>865</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
+        <v>888</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>889</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>890</v>
-      </c>
       <c r="C18" s="18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
+        <v>890</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>891</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>892</v>
-      </c>
       <c r="C19" s="18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
+        <v>892</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>893</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>894</v>
-      </c>
       <c r="C20" s="18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
+        <v>894</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>895</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>896</v>
-      </c>
       <c r="C21" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
+        <v>896</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>897</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="C22" s="18" t="s">
         <v>898</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="D22" s="18" t="s">
         <v>899</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="E22" s="18" t="s">
+        <v>857</v>
+      </c>
+      <c r="F22" s="18" t="s">
         <v>900</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
+        <v>901</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>902</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="C23" s="18" t="s">
+        <v>898</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>899</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>857</v>
+      </c>
+      <c r="F23" s="18" t="s">
         <v>903</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>899</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>900</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
+        <v>904</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>905</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="C24" s="18" t="s">
         <v>906</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="D24" s="18" t="s">
         <v>907</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="E24" s="18" t="s">
+        <v>864</v>
+      </c>
+      <c r="F24" s="18" t="s">
         <v>908</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>865</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
+        <v>909</v>
+      </c>
+      <c r="B25" s="18" t="s">
         <v>910</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="C25" s="18" t="s">
+        <v>655</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>857</v>
+      </c>
+      <c r="F25" s="18" t="s">
         <v>911</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>656</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>614</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
+        <v>912</v>
+      </c>
+      <c r="B26" s="18" t="s">
         <v>913</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="C26" s="18" t="s">
+        <v>497</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>857</v>
+      </c>
+      <c r="F26" s="18" t="s">
         <v>914</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>498</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>467</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
+        <v>915</v>
+      </c>
+      <c r="B27" s="18" t="s">
         <v>916</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>917</v>
-      </c>
       <c r="C27" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
+        <v>917</v>
+      </c>
+      <c r="B28" s="18" t="s">
         <v>918</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>919</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>155</v>
@@ -10658,210 +10655,210 @@
         <v>151</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
+        <v>920</v>
+      </c>
+      <c r="B29" s="18" t="s">
         <v>921</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="C29" s="18" t="s">
         <v>922</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>923</v>
-      </c>
       <c r="D29" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
+        <v>923</v>
+      </c>
+      <c r="B30" s="18" t="s">
         <v>924</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="C30" s="18" t="s">
         <v>925</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>926</v>
-      </c>
       <c r="D30" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
+        <v>926</v>
+      </c>
+      <c r="B31" s="18" t="s">
         <v>927</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="C31" s="18" t="s">
         <v>928</v>
       </c>
-      <c r="C31" s="18" t="s">
-        <v>929</v>
-      </c>
       <c r="D31" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
+        <v>929</v>
+      </c>
+      <c r="B32" s="18" t="s">
         <v>930</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="C32" s="18" t="s">
         <v>931</v>
       </c>
-      <c r="C32" s="18" t="s">
-        <v>932</v>
-      </c>
       <c r="D32" s="18" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
+        <v>932</v>
+      </c>
+      <c r="B33" s="18" t="s">
         <v>933</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="C33" s="18" t="s">
         <v>934</v>
       </c>
-      <c r="C33" s="18" t="s">
-        <v>935</v>
-      </c>
       <c r="D33" s="18" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
+        <v>935</v>
+      </c>
+      <c r="B34" s="18" t="s">
         <v>936</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>937</v>
-      </c>
       <c r="C34" s="18" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
+        <v>937</v>
+      </c>
+      <c r="B35" s="18" t="s">
         <v>938</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="C35" s="18" t="s">
         <v>939</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="D35" s="18" t="s">
         <v>940</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="E35" s="18" t="s">
         <v>941</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="F35" s="18" t="s">
         <v>942</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
+        <v>943</v>
+      </c>
+      <c r="B36" s="18" t="s">
         <v>944</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="C36" s="18" t="s">
         <v>945</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="D36" s="18" t="s">
+        <v>940</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>941</v>
+      </c>
+      <c r="F36" s="18" t="s">
         <v>946</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>941</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>942</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
+        <v>947</v>
+      </c>
+      <c r="B37" s="18" t="s">
         <v>948</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="C37" s="18" t="s">
         <v>949</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="D37" s="18" t="s">
+        <v>940</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>941</v>
+      </c>
+      <c r="F37" s="18" t="s">
         <v>950</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>941</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>942</v>
-      </c>
-      <c r="F37" s="18" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
+        <v>951</v>
+      </c>
+      <c r="B38" s="18" t="s">
         <v>952</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="C38" s="18" t="s">
         <v>953</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="D38" s="18" t="s">
+        <v>940</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>941</v>
+      </c>
+      <c r="F38" s="18" t="s">
         <v>954</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>941</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>942</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>955</v>
       </c>
     </row>
   </sheetData>
